--- a/1.BlindTest/XII/BTXIIB/BTXIIB.xlsx
+++ b/1.BlindTest/XII/BTXIIB/BTXIIB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lspri\Dropbox (UCL)\Temporary Folder for Github\1.BlindTest\XII\BTXIIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA5F92EA-1DB4-48AA-ABEE-78B3320F3132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FD69E4F-A201-4BC0-9089-9B063C168AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6053D40E-8A20-42E0-AD37-38BB8AE1C208}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2FC9BA1-260C-4EF0-B965-E5749A5B40E7}"/>
   </bookViews>
   <sheets>
     <sheet name="BTXIIB_forxls" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="357">
   <si>
     <t>Filename</t>
   </si>
   <si>
+    <t>Density 1 /gcm-3</t>
+  </si>
+  <si>
+    <t>Lattice Energy 1 /kJmol-1</t>
+  </si>
+  <si>
+    <t>Packing Coefficient 1</t>
+  </si>
+  <si>
     <t>Space Group</t>
   </si>
   <si>
@@ -1082,9 +1091,6 @@
   </si>
   <si>
     <t>AXOSOW_cis_as9</t>
-  </si>
-  <si>
-    <t>AXOSOW_spf_</t>
   </si>
 </sst>
 </file>
@@ -1944,33 +1950,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B9DC24-052A-4D75-B00B-3BA10C30BB20}">
-  <dimension ref="A1:F332"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204808F3-12AC-445D-94EB-BA7C40E85564}">
+  <dimension ref="A1:F331"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
-        <v>1.084133</v>
-      </c>
-      <c r="C1">
-        <v>-35.933</v>
-      </c>
-      <c r="D1">
-        <v>0.69279199999999996</v>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>1.0716509999999999</v>
@@ -1982,15 +1988,15 @@
         <v>0.67759899999999995</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>1.1297969999999999</v>
@@ -2002,12 +2008,12 @@
         <v>0.72054499999999999</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>1.1204240000000001</v>
@@ -2019,12 +2025,12 @@
         <v>0.70896499999999996</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>1.10328</v>
@@ -2036,12 +2042,12 @@
         <v>0.70363399999999998</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>1.0856319999999999</v>
@@ -2053,12 +2059,12 @@
         <v>0.69172400000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>1.1085130000000001</v>
@@ -2070,12 +2076,12 @@
         <v>0.69679800000000003</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1.0891839999999999</v>
@@ -2087,12 +2093,12 @@
         <v>0.687948</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>1.121661</v>
@@ -2104,12 +2110,12 @@
         <v>0.70580200000000004</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>1.1016649999999999</v>
@@ -2121,12 +2127,12 @@
         <v>0.69640500000000005</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>1.0823339999999999</v>
@@ -2138,12 +2144,12 @@
         <v>0.68805499999999997</v>
       </c>
       <c r="E11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>1.114495</v>
@@ -2155,12 +2161,12 @@
         <v>0.70829699999999995</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>1.112803</v>
@@ -2172,12 +2178,12 @@
         <v>0.70988399999999996</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>1.095674</v>
@@ -2189,12 +2195,12 @@
         <v>0.69476700000000002</v>
       </c>
       <c r="E14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>1.094122</v>
@@ -2206,12 +2212,12 @@
         <v>0.69040000000000001</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>1.1036600000000001</v>
@@ -2223,12 +2229,12 @@
         <v>0.69672299999999998</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>1.1020700000000001</v>
@@ -2240,12 +2246,12 @@
         <v>0.697801</v>
       </c>
       <c r="E17" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>1.094722</v>
@@ -2257,12 +2263,12 @@
         <v>0.69400799999999996</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>1.067094</v>
@@ -2274,12 +2280,12 @@
         <v>0.68017000000000005</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>1.0891770000000001</v>
@@ -2291,12 +2297,12 @@
         <v>0.68819900000000001</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>1.103931</v>
@@ -2308,12 +2314,12 @@
         <v>0.69855999999999996</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B22">
         <v>1.0876479999999999</v>
@@ -2325,12 +2331,12 @@
         <v>0.69097799999999998</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B23">
         <v>1.0917079999999999</v>
@@ -2342,12 +2348,12 @@
         <v>0.68686800000000003</v>
       </c>
       <c r="E23" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B24">
         <v>1.0987899999999999</v>
@@ -2359,12 +2365,12 @@
         <v>0.69612399999999997</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B25">
         <v>1.104293</v>
@@ -2376,12 +2382,12 @@
         <v>0.70064000000000004</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B26">
         <v>1.1038779999999999</v>
@@ -2393,12 +2399,12 @@
         <v>0.69379800000000003</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B27">
         <v>1.094563</v>
@@ -2410,12 +2416,12 @@
         <v>0.688859</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B28">
         <v>1.097585</v>
@@ -2427,12 +2433,12 @@
         <v>0.700847</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B29">
         <v>1.0941940000000001</v>
@@ -2444,12 +2450,12 @@
         <v>0.69683799999999996</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B30">
         <v>1.125427</v>
@@ -2461,12 +2467,12 @@
         <v>0.70773600000000003</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>1.0724929999999999</v>
@@ -2478,12 +2484,12 @@
         <v>0.67868600000000001</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B32">
         <v>1.099877</v>
@@ -2495,12 +2501,12 @@
         <v>0.69560200000000005</v>
       </c>
       <c r="E32" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B33">
         <v>1.094355</v>
@@ -2512,12 +2518,12 @@
         <v>0.696573</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B34">
         <v>1.0952710000000001</v>
@@ -2529,12 +2535,12 @@
         <v>0.69300700000000004</v>
       </c>
       <c r="E34" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B35">
         <v>1.076101</v>
@@ -2546,12 +2552,12 @@
         <v>0.68220000000000003</v>
       </c>
       <c r="E35" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B36">
         <v>1.0845149999999999</v>
@@ -2563,12 +2569,12 @@
         <v>0.68335000000000001</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B37">
         <v>1.088576</v>
@@ -2580,12 +2586,12 @@
         <v>0.69668200000000002</v>
       </c>
       <c r="E37" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B38">
         <v>1.09883</v>
@@ -2597,12 +2603,12 @@
         <v>0.70089500000000005</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B39">
         <v>1.087774</v>
@@ -2614,12 +2620,12 @@
         <v>0.68523100000000003</v>
       </c>
       <c r="E39" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B40">
         <v>1.091011</v>
@@ -2631,12 +2637,12 @@
         <v>0.69014600000000004</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B41">
         <v>1.101558</v>
@@ -2648,12 +2654,12 @@
         <v>0.69480699999999995</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B42">
         <v>1.111302</v>
@@ -2665,12 +2671,12 @@
         <v>0.706565</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B43">
         <v>1.125583</v>
@@ -2682,12 +2688,12 @@
         <v>0.71226199999999995</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B44">
         <v>1.0860099999999999</v>
@@ -2699,12 +2705,12 @@
         <v>0.68285899999999999</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B45">
         <v>1.092549</v>
@@ -2716,12 +2722,12 @@
         <v>0.689272</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B46">
         <v>1.0590679999999999</v>
@@ -2733,12 +2739,12 @@
         <v>0.67470399999999997</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B47">
         <v>1.0764720000000001</v>
@@ -2750,12 +2756,12 @@
         <v>0.68191299999999999</v>
       </c>
       <c r="E47" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B48">
         <v>1.09009</v>
@@ -2767,12 +2773,12 @@
         <v>0.69112700000000005</v>
       </c>
       <c r="E48" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B49">
         <v>1.084352</v>
@@ -2784,12 +2790,12 @@
         <v>0.69203599999999998</v>
       </c>
       <c r="E49" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B50">
         <v>1.086346</v>
@@ -2801,12 +2807,12 @@
         <v>0.690774</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B51">
         <v>1.0930580000000001</v>
@@ -2818,12 +2824,12 @@
         <v>0.68788300000000002</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B52">
         <v>1.09714</v>
@@ -2835,12 +2841,12 @@
         <v>0.69550699999999999</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B53">
         <v>1.097181</v>
@@ -2852,12 +2858,12 @@
         <v>0.68823100000000004</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B54">
         <v>1.0887249999999999</v>
@@ -2869,12 +2875,12 @@
         <v>0.68335999999999997</v>
       </c>
       <c r="E54" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B55">
         <v>1.1142920000000001</v>
@@ -2886,12 +2892,12 @@
         <v>0.70726100000000003</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B56">
         <v>1.1121890000000001</v>
@@ -2903,12 +2909,12 @@
         <v>0.69902399999999998</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B57">
         <v>1.089288</v>
@@ -2920,12 +2926,12 @@
         <v>0.68585700000000005</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B58">
         <v>1.0827599999999999</v>
@@ -2937,12 +2943,12 @@
         <v>0.67839700000000003</v>
       </c>
       <c r="E58" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B59">
         <v>1.089766</v>
@@ -2954,12 +2960,12 @@
         <v>0.68936299999999995</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B60">
         <v>1.108735</v>
@@ -2971,12 +2977,12 @@
         <v>0.69722200000000001</v>
       </c>
       <c r="E60" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B61">
         <v>1.0847850000000001</v>
@@ -2988,12 +2994,12 @@
         <v>0.68527499999999997</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B62">
         <v>1.0969640000000001</v>
@@ -3005,12 +3011,12 @@
         <v>0.69286700000000001</v>
       </c>
       <c r="E62" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B63">
         <v>1.0972900000000001</v>
@@ -3022,12 +3028,12 @@
         <v>0.69361200000000001</v>
       </c>
       <c r="E63" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B64">
         <v>1.0988290000000001</v>
@@ -3039,12 +3045,12 @@
         <v>0.69129799999999997</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B65">
         <v>1.10205</v>
@@ -3056,12 +3062,12 @@
         <v>0.69530999999999998</v>
       </c>
       <c r="E65" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B66">
         <v>1.0790329999999999</v>
@@ -3073,12 +3079,12 @@
         <v>0.68164199999999997</v>
       </c>
       <c r="E66" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B67">
         <v>1.053094</v>
@@ -3090,12 +3096,12 @@
         <v>0.66211200000000003</v>
       </c>
       <c r="E67" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B68">
         <v>1.0959449999999999</v>
@@ -3107,12 +3113,12 @@
         <v>0.69054199999999999</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B69">
         <v>1.114414</v>
@@ -3124,12 +3130,12 @@
         <v>0.70027700000000004</v>
       </c>
       <c r="E69" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B70">
         <v>1.0763510000000001</v>
@@ -3141,12 +3147,12 @@
         <v>0.68304500000000001</v>
       </c>
       <c r="E70" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B71">
         <v>1.08639</v>
@@ -3158,12 +3164,12 @@
         <v>0.68586800000000003</v>
       </c>
       <c r="E71" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B72">
         <v>1.091083</v>
@@ -3175,12 +3181,12 @@
         <v>0.68861300000000003</v>
       </c>
       <c r="E72" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B73">
         <v>1.0777399999999999</v>
@@ -3192,12 +3198,12 @@
         <v>0.68369500000000005</v>
       </c>
       <c r="E73" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B74">
         <v>1.061715</v>
@@ -3209,12 +3215,12 @@
         <v>0.67483099999999996</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B75">
         <v>1.0767679999999999</v>
@@ -3226,12 +3232,12 @@
         <v>0.68862299999999999</v>
       </c>
       <c r="E75" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B76">
         <v>1.101297</v>
@@ -3243,12 +3249,12 @@
         <v>0.69780900000000001</v>
       </c>
       <c r="E76" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B77">
         <v>1.0339</v>
@@ -3260,12 +3266,12 @@
         <v>0.65297099999999997</v>
       </c>
       <c r="E77" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B78">
         <v>1.0730569999999999</v>
@@ -3277,12 +3283,12 @@
         <v>0.67641099999999998</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B79">
         <v>1.0960730000000001</v>
@@ -3294,12 +3300,12 @@
         <v>0.69169199999999997</v>
       </c>
       <c r="E79" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B80">
         <v>1.0746070000000001</v>
@@ -3311,12 +3317,12 @@
         <v>0.67528500000000002</v>
       </c>
       <c r="E80" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B81">
         <v>1.098671</v>
@@ -3328,12 +3334,12 @@
         <v>0.69633999999999996</v>
       </c>
       <c r="E81" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B82">
         <v>1.0948199999999999</v>
@@ -3345,12 +3351,12 @@
         <v>0.69558399999999998</v>
       </c>
       <c r="E82" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B83">
         <v>1.059804</v>
@@ -3362,12 +3368,12 @@
         <v>0.66740500000000003</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B84">
         <v>1.0974900000000001</v>
@@ -3379,12 +3385,12 @@
         <v>0.69333</v>
       </c>
       <c r="E84" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B85">
         <v>1.0926800000000001</v>
@@ -3396,12 +3402,12 @@
         <v>0.68618800000000002</v>
       </c>
       <c r="E85" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B86">
         <v>1.0657669999999999</v>
@@ -3413,12 +3419,12 @@
         <v>0.67542800000000003</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B87">
         <v>1.0952409999999999</v>
@@ -3430,12 +3436,12 @@
         <v>0.69012300000000004</v>
       </c>
       <c r="E87" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B88">
         <v>1.098641</v>
@@ -3447,12 +3453,12 @@
         <v>0.69634499999999999</v>
       </c>
       <c r="E88" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B89">
         <v>1.1001270000000001</v>
@@ -3464,12 +3470,12 @@
         <v>0.69053799999999999</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B90">
         <v>1.0851500000000001</v>
@@ -3481,12 +3487,12 @@
         <v>0.68631600000000004</v>
       </c>
       <c r="E90" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B91">
         <v>1.0907100000000001</v>
@@ -3498,12 +3504,12 @@
         <v>0.69654099999999997</v>
       </c>
       <c r="E91" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B92">
         <v>1.072659</v>
@@ -3515,12 +3521,12 @@
         <v>0.67240599999999995</v>
       </c>
       <c r="E92" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B93">
         <v>1.089485</v>
@@ -3532,12 +3538,12 @@
         <v>0.68513599999999997</v>
       </c>
       <c r="E93" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B94">
         <v>1.100519</v>
@@ -3549,12 +3555,12 @@
         <v>0.69990699999999995</v>
       </c>
       <c r="E94" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B95">
         <v>1.098611</v>
@@ -3566,12 +3572,12 @@
         <v>0.69590399999999997</v>
       </c>
       <c r="E95" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B96">
         <v>1.089018</v>
@@ -3583,12 +3589,12 @@
         <v>0.68923299999999998</v>
       </c>
       <c r="E96" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B97">
         <v>1.0488390000000001</v>
@@ -3600,12 +3606,12 @@
         <v>0.65688599999999997</v>
       </c>
       <c r="E97" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B98">
         <v>1.115221</v>
@@ -3617,12 +3623,12 @@
         <v>0.70759099999999997</v>
       </c>
       <c r="E98" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B99">
         <v>1.0806899999999999</v>
@@ -3634,12 +3640,12 @@
         <v>0.68364400000000003</v>
       </c>
       <c r="E99" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B100">
         <v>1.0949260000000001</v>
@@ -3651,12 +3657,12 @@
         <v>0.695137</v>
       </c>
       <c r="E100" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B101">
         <v>1.103148</v>
@@ -3668,12 +3674,12 @@
         <v>0.69623800000000002</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B102">
         <v>1.0810919999999999</v>
@@ -3685,12 +3691,12 @@
         <v>0.68558200000000002</v>
       </c>
       <c r="E102" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B103">
         <v>1.0953360000000001</v>
@@ -3702,12 +3708,12 @@
         <v>0.69109699999999996</v>
       </c>
       <c r="E103" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B104">
         <v>1.080303</v>
@@ -3719,12 +3725,12 @@
         <v>0.68139700000000003</v>
       </c>
       <c r="E104" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B105">
         <v>1.071027</v>
@@ -3736,12 +3742,12 @@
         <v>0.67676800000000004</v>
       </c>
       <c r="E105" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B106">
         <v>1.0890150000000001</v>
@@ -3753,12 +3759,12 @@
         <v>0.68581099999999995</v>
       </c>
       <c r="E106" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B107">
         <v>1.0789550000000001</v>
@@ -3770,12 +3776,12 @@
         <v>0.68307499999999999</v>
       </c>
       <c r="E107" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B108">
         <v>1.09076</v>
@@ -3787,12 +3793,12 @@
         <v>0.68875299999999995</v>
       </c>
       <c r="E108" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B109">
         <v>1.09124</v>
@@ -3804,12 +3810,12 @@
         <v>0.69525800000000004</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B110">
         <v>1.0743990000000001</v>
@@ -3821,12 +3827,12 @@
         <v>0.67921500000000001</v>
       </c>
       <c r="E110" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B111">
         <v>1.079002</v>
@@ -3838,12 +3844,12 @@
         <v>0.68115199999999998</v>
       </c>
       <c r="E111" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B112">
         <v>1.069728</v>
@@ -3855,12 +3861,12 @@
         <v>0.673871</v>
       </c>
       <c r="E112" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B113">
         <v>1.07843</v>
@@ -3872,12 +3878,12 @@
         <v>0.67749199999999998</v>
       </c>
       <c r="E113" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B114">
         <v>1.057372</v>
@@ -3889,12 +3895,12 @@
         <v>0.66243099999999999</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B115">
         <v>1.079229</v>
@@ -3906,12 +3912,12 @@
         <v>0.67585700000000004</v>
       </c>
       <c r="E115" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B116">
         <v>1.0602799999999999</v>
@@ -3923,12 +3929,12 @@
         <v>0.66920000000000002</v>
       </c>
       <c r="E116" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B117">
         <v>1.076592</v>
@@ -3940,12 +3946,12 @@
         <v>0.68284299999999998</v>
       </c>
       <c r="E117" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B118">
         <v>1.0834699999999999</v>
@@ -3957,12 +3963,12 @@
         <v>0.68509600000000004</v>
       </c>
       <c r="E118" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B119">
         <v>1.094492</v>
@@ -3974,12 +3980,12 @@
         <v>0.68898700000000002</v>
       </c>
       <c r="E119" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B120">
         <v>1.0883989999999999</v>
@@ -3991,12 +3997,12 @@
         <v>0.69255</v>
       </c>
       <c r="E120" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B121">
         <v>1.0897380000000001</v>
@@ -4008,12 +4014,12 @@
         <v>0.68594599999999994</v>
       </c>
       <c r="E121" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B122">
         <v>1.0530679999999999</v>
@@ -4025,12 +4031,12 @@
         <v>0.66567699999999996</v>
       </c>
       <c r="E122" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B123">
         <v>1.0419799999999999</v>
@@ -4042,12 +4048,12 @@
         <v>0.65935100000000002</v>
       </c>
       <c r="E123" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B124">
         <v>1.0962050000000001</v>
@@ -4059,12 +4065,12 @@
         <v>0.69079999999999997</v>
       </c>
       <c r="E124" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B125">
         <v>1.072303</v>
@@ -4076,12 +4082,12 @@
         <v>0.67921600000000004</v>
       </c>
       <c r="E125" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B126">
         <v>1.0544469999999999</v>
@@ -4093,12 +4099,12 @@
         <v>0.668049</v>
       </c>
       <c r="E126" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B127">
         <v>1.087909</v>
@@ -4110,12 +4116,12 @@
         <v>0.68911999999999995</v>
       </c>
       <c r="E127" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B128">
         <v>1.0643499999999999</v>
@@ -4127,12 +4133,12 @@
         <v>0.67318100000000003</v>
       </c>
       <c r="E128" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B129">
         <v>1.064792</v>
@@ -4144,12 +4150,12 @@
         <v>0.67318100000000003</v>
       </c>
       <c r="E129" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B130">
         <v>1.0805849999999999</v>
@@ -4161,12 +4167,12 @@
         <v>0.68416200000000005</v>
       </c>
       <c r="E130" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B131">
         <v>1.1030899999999999</v>
@@ -4178,12 +4184,12 @@
         <v>0.69696999999999998</v>
       </c>
       <c r="E131" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B132">
         <v>1.0717000000000001</v>
@@ -4195,12 +4201,12 @@
         <v>0.675265</v>
       </c>
       <c r="E132" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B133">
         <v>1.074025</v>
@@ -4212,12 +4218,12 @@
         <v>0.68096100000000004</v>
       </c>
       <c r="E133" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B134">
         <v>1.083167</v>
@@ -4229,12 +4235,12 @@
         <v>0.68226500000000001</v>
       </c>
       <c r="E134" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B135">
         <v>1.0783199999999999</v>
@@ -4246,12 +4252,12 @@
         <v>0.67561000000000004</v>
       </c>
       <c r="E135" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B136">
         <v>1.066147</v>
@@ -4263,12 +4269,12 @@
         <v>0.66995199999999999</v>
       </c>
       <c r="E136" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B137">
         <v>1.086422</v>
@@ -4280,12 +4286,12 @@
         <v>0.68701699999999999</v>
       </c>
       <c r="E137" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B138">
         <v>1.069653</v>
@@ -4297,12 +4303,12 @@
         <v>0.67212099999999997</v>
       </c>
       <c r="E138" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B139">
         <v>1.059858</v>
@@ -4314,12 +4320,12 @@
         <v>0.67454700000000001</v>
       </c>
       <c r="E139" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B140">
         <v>1.0620430000000001</v>
@@ -4331,12 +4337,12 @@
         <v>0.67133699999999996</v>
       </c>
       <c r="E140" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B141">
         <v>1.098355</v>
@@ -4348,12 +4354,12 @@
         <v>0.70203899999999997</v>
       </c>
       <c r="E141" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B142">
         <v>1.0529390000000001</v>
@@ -4365,12 +4371,12 @@
         <v>0.66757599999999995</v>
       </c>
       <c r="E142" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B143">
         <v>1.0596890000000001</v>
@@ -4382,12 +4388,12 @@
         <v>0.67</v>
       </c>
       <c r="E143" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B144">
         <v>1.0631600000000001</v>
@@ -4399,12 +4405,12 @@
         <v>0.67362100000000003</v>
       </c>
       <c r="E144" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B145">
         <v>1.0438050000000001</v>
@@ -4416,12 +4422,12 @@
         <v>0.660443</v>
       </c>
       <c r="E145" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B146">
         <v>0.97956900000000002</v>
@@ -4433,12 +4439,12 @@
         <v>0.61794899999999997</v>
       </c>
       <c r="E146" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B147">
         <v>1.0538700000000001</v>
@@ -4450,12 +4456,12 @@
         <v>0.67315499999999995</v>
       </c>
       <c r="E147" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B148">
         <v>1.0680559999999999</v>
@@ -4467,12 +4473,12 @@
         <v>0.67471199999999998</v>
       </c>
       <c r="E148" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B149">
         <v>1.09172</v>
@@ -4484,12 +4490,12 @@
         <v>0.68982600000000005</v>
       </c>
       <c r="E149" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B150">
         <v>1.0817939999999999</v>
@@ -4501,12 +4507,12 @@
         <v>0.68351899999999999</v>
       </c>
       <c r="E150" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B151">
         <v>1.0687249999999999</v>
@@ -4518,12 +4524,12 @@
         <v>0.67732000000000003</v>
       </c>
       <c r="E151" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B152">
         <v>1.0521940000000001</v>
@@ -4535,12 +4541,12 @@
         <v>0.66578800000000005</v>
       </c>
       <c r="E152" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B153">
         <v>1.0863799999999999</v>
@@ -4552,12 +4558,12 @@
         <v>0.68323100000000003</v>
       </c>
       <c r="E153" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B154">
         <v>1.049282</v>
@@ -4569,12 +4575,12 @@
         <v>0.66427700000000001</v>
       </c>
       <c r="E154" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B155">
         <v>1.0446470000000001</v>
@@ -4586,12 +4592,12 @@
         <v>0.66015100000000004</v>
       </c>
       <c r="E155" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B156">
         <v>1.0382229999999999</v>
@@ -4603,12 +4609,12 @@
         <v>0.65748499999999999</v>
       </c>
       <c r="E156" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B157">
         <v>1.078449</v>
@@ -4620,12 +4626,12 @@
         <v>0.67955500000000002</v>
       </c>
       <c r="E157" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B158">
         <v>1.0561240000000001</v>
@@ -4637,12 +4643,12 @@
         <v>0.66832000000000003</v>
       </c>
       <c r="E158" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B159">
         <v>1.0246949999999999</v>
@@ -4654,12 +4660,12 @@
         <v>0.64618500000000001</v>
       </c>
       <c r="E159" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B160">
         <v>1.0728249999999999</v>
@@ -4671,12 +4677,12 @@
         <v>0.67592099999999999</v>
       </c>
       <c r="E160" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B161">
         <v>1.0262739999999999</v>
@@ -4688,12 +4694,12 @@
         <v>0.64568499999999995</v>
       </c>
       <c r="E161" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B162">
         <v>1.0652509999999999</v>
@@ -4705,12 +4711,12 @@
         <v>0.67050699999999996</v>
       </c>
       <c r="E162" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B163">
         <v>1.0512950000000001</v>
@@ -4722,12 +4728,12 @@
         <v>0.66459400000000002</v>
       </c>
       <c r="E163" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B164">
         <v>1.0548420000000001</v>
@@ -4739,12 +4745,12 @@
         <v>0.66435900000000003</v>
       </c>
       <c r="E164" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B165">
         <v>1.0524720000000001</v>
@@ -4756,12 +4762,12 @@
         <v>0.66628600000000004</v>
       </c>
       <c r="E165" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B166">
         <v>1.0341819999999999</v>
@@ -4773,12 +4779,12 @@
         <v>0.65438300000000005</v>
       </c>
       <c r="E166" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B167">
         <v>1.0501579999999999</v>
@@ -4790,12 +4796,12 @@
         <v>0.67068700000000003</v>
       </c>
       <c r="E167" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B168">
         <v>1.0639540000000001</v>
@@ -4807,12 +4813,12 @@
         <v>0.67205899999999996</v>
       </c>
       <c r="E168" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B169">
         <v>1.027585</v>
@@ -4824,12 +4830,12 @@
         <v>0.65175899999999998</v>
       </c>
       <c r="E169" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B170">
         <v>1.0302340000000001</v>
@@ -4841,12 +4847,12 @@
         <v>0.65361599999999997</v>
       </c>
       <c r="E170" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B171">
         <v>1.0460100000000001</v>
@@ -4858,12 +4864,12 @@
         <v>0.66398100000000004</v>
       </c>
       <c r="E171" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B172">
         <v>1.054389</v>
@@ -4875,12 +4881,12 @@
         <v>0.66881199999999996</v>
       </c>
       <c r="E172" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B173">
         <v>1.0508919999999999</v>
@@ -4892,12 +4898,12 @@
         <v>0.66117199999999998</v>
       </c>
       <c r="E173" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B174">
         <v>1.036084</v>
@@ -4909,12 +4915,12 @@
         <v>0.65663400000000005</v>
       </c>
       <c r="E174" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B175">
         <v>1.1303240000000001</v>
@@ -4926,12 +4932,12 @@
         <v>0.71353999999999995</v>
       </c>
       <c r="E175" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B176">
         <v>1.080174</v>
@@ -4943,12 +4949,12 @@
         <v>0.68348200000000003</v>
       </c>
       <c r="E176" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B177">
         <v>1.0520780000000001</v>
@@ -4960,12 +4966,12 @@
         <v>0.66713</v>
       </c>
       <c r="E177" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B178">
         <v>1.112177</v>
@@ -4977,12 +4983,12 @@
         <v>0.70367100000000005</v>
       </c>
       <c r="E178" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B179">
         <v>1.0699920000000001</v>
@@ -4994,12 +5000,12 @@
         <v>0.67642800000000003</v>
       </c>
       <c r="E179" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B180">
         <v>1.00871</v>
@@ -5011,12 +5017,12 @@
         <v>0.63342200000000004</v>
       </c>
       <c r="E180" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B181">
         <v>1.07162</v>
@@ -5028,12 +5034,12 @@
         <v>0.67954999999999999</v>
       </c>
       <c r="E181" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B182">
         <v>1.085914</v>
@@ -5045,12 +5051,12 @@
         <v>0.68850599999999995</v>
       </c>
       <c r="E182" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B183">
         <v>1.098255</v>
@@ -5062,12 +5068,12 @@
         <v>0.69734399999999996</v>
       </c>
       <c r="E183" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B184">
         <v>1.004041</v>
@@ -5079,12 +5085,12 @@
         <v>0.63656100000000004</v>
       </c>
       <c r="E184" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B185">
         <v>1.089704</v>
@@ -5096,12 +5102,12 @@
         <v>0.69616599999999995</v>
       </c>
       <c r="E185" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B186">
         <v>1.0887519999999999</v>
@@ -5113,12 +5119,12 @@
         <v>0.69119799999999998</v>
       </c>
       <c r="E186" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B187">
         <v>0.96803300000000003</v>
@@ -5130,12 +5136,12 @@
         <v>0.60975500000000005</v>
       </c>
       <c r="E187" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B188">
         <v>1.0919099999999999</v>
@@ -5147,12 +5153,12 @@
         <v>0.69211999999999996</v>
       </c>
       <c r="E188" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B189">
         <v>1.095458</v>
@@ -5164,12 +5170,12 @@
         <v>0.69133199999999995</v>
       </c>
       <c r="E189" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B190">
         <v>1.108341</v>
@@ -5181,12 +5187,12 @@
         <v>0.70337499999999997</v>
       </c>
       <c r="E190" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B191">
         <v>1.107254</v>
@@ -5198,12 +5204,12 @@
         <v>0.70648599999999995</v>
       </c>
       <c r="E191" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B192">
         <v>1.0745100000000001</v>
@@ -5215,12 +5221,12 @@
         <v>0.68132400000000004</v>
       </c>
       <c r="E192" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B193">
         <v>1.082622</v>
@@ -5232,12 +5238,12 @@
         <v>0.68701999999999996</v>
       </c>
       <c r="E193" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B194">
         <v>1.1015550000000001</v>
@@ -5249,12 +5255,12 @@
         <v>0.69698400000000005</v>
       </c>
       <c r="E194" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B195">
         <v>1.084133</v>
@@ -5266,12 +5272,12 @@
         <v>0.69279199999999996</v>
       </c>
       <c r="E195" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B196">
         <v>1.0844199999999999</v>
@@ -5283,12 +5289,12 @@
         <v>0.68234300000000003</v>
       </c>
       <c r="E196" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B197">
         <v>1.0817209999999999</v>
@@ -5300,12 +5306,12 @@
         <v>0.683195</v>
       </c>
       <c r="E197" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B198">
         <v>1.0736760000000001</v>
@@ -5317,12 +5323,12 @@
         <v>0.68129499999999998</v>
       </c>
       <c r="E198" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B199">
         <v>1.1027629999999999</v>
@@ -5334,12 +5340,12 @@
         <v>0.70001100000000005</v>
       </c>
       <c r="E199" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B200">
         <v>1.096042</v>
@@ -5351,12 +5357,12 @@
         <v>0.69796599999999998</v>
       </c>
       <c r="E200" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B201">
         <v>1.0831679999999999</v>
@@ -5368,12 +5374,12 @@
         <v>0.68458300000000005</v>
       </c>
       <c r="E201" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B202">
         <v>1.0705690000000001</v>
@@ -5385,12 +5391,12 @@
         <v>0.67815800000000004</v>
       </c>
       <c r="E202" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B203">
         <v>1.1289530000000001</v>
@@ -5402,12 +5408,12 @@
         <v>0.71948500000000004</v>
       </c>
       <c r="E203" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B204">
         <v>1.083361</v>
@@ -5419,12 +5425,12 @@
         <v>0.68559999999999999</v>
       </c>
       <c r="E204" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B205">
         <v>1.0921190000000001</v>
@@ -5436,12 +5442,12 @@
         <v>0.68849300000000002</v>
       </c>
       <c r="E205" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B206">
         <v>1.074786</v>
@@ -5453,12 +5459,12 @@
         <v>0.68358799999999997</v>
       </c>
       <c r="E206" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B207">
         <v>1.0872299999999999</v>
@@ -5470,12 +5476,12 @@
         <v>0.68989400000000001</v>
       </c>
       <c r="E207" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B208">
         <v>0.94808700000000001</v>
@@ -5487,12 +5493,12 @@
         <v>0.59807100000000002</v>
       </c>
       <c r="E208" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B209">
         <v>1.0977460000000001</v>
@@ -5504,12 +5510,12 @@
         <v>0.697658</v>
       </c>
       <c r="E209" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B210">
         <v>1.0824260000000001</v>
@@ -5521,12 +5527,12 @@
         <v>0.68744499999999997</v>
       </c>
       <c r="E210" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B211">
         <v>1.0932729999999999</v>
@@ -5538,12 +5544,12 @@
         <v>0.69018699999999999</v>
       </c>
       <c r="E211" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B212">
         <v>1.1050519999999999</v>
@@ -5555,12 +5561,12 @@
         <v>0.70410799999999996</v>
       </c>
       <c r="E212" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B213">
         <v>1.081971</v>
@@ -5572,12 +5578,12 @@
         <v>0.69077999999999995</v>
       </c>
       <c r="E213" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B214">
         <v>1.0901540000000001</v>
@@ -5589,12 +5595,12 @@
         <v>0.69421999999999995</v>
       </c>
       <c r="E214" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B215">
         <v>1.067906</v>
@@ -5606,12 +5612,12 @@
         <v>0.68141099999999999</v>
       </c>
       <c r="E215" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B216">
         <v>1.070068</v>
@@ -5623,12 +5629,12 @@
         <v>0.67865600000000004</v>
       </c>
       <c r="E216" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B217">
         <v>1.0572429999999999</v>
@@ -5640,12 +5646,12 @@
         <v>0.66969500000000004</v>
       </c>
       <c r="E217" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B218">
         <v>1.0746039999999999</v>
@@ -5657,12 +5663,12 @@
         <v>0.68218999999999996</v>
       </c>
       <c r="E218" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B219">
         <v>1.0617110000000001</v>
@@ -5674,12 +5680,12 @@
         <v>0.66715599999999997</v>
       </c>
       <c r="E219" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B220">
         <v>1.1045640000000001</v>
@@ -5691,12 +5697,12 @@
         <v>0.69951399999999997</v>
       </c>
       <c r="E220" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B221">
         <v>1.0855539999999999</v>
@@ -5708,12 +5714,12 @@
         <v>0.6885</v>
       </c>
       <c r="E221" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B222">
         <v>1.0590299999999999</v>
@@ -5725,12 +5731,12 @@
         <v>0.67487799999999998</v>
       </c>
       <c r="E222" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B223">
         <v>1.0851</v>
@@ -5742,12 +5748,12 @@
         <v>0.68417300000000003</v>
       </c>
       <c r="E223" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B224">
         <v>1.073197</v>
@@ -5759,12 +5765,12 @@
         <v>0.68169199999999996</v>
       </c>
       <c r="E224" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B225">
         <v>1.0414220000000001</v>
@@ -5776,12 +5782,12 @@
         <v>0.65600499999999995</v>
       </c>
       <c r="E225" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B226">
         <v>1.088697</v>
@@ -5793,12 +5799,12 @@
         <v>0.68811900000000004</v>
       </c>
       <c r="E226" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B227">
         <v>1.0914360000000001</v>
@@ -5810,12 +5816,12 @@
         <v>0.69139799999999996</v>
       </c>
       <c r="E227" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B228">
         <v>1.066392</v>
@@ -5827,12 +5833,12 @@
         <v>0.67005300000000001</v>
       </c>
       <c r="E228" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B229">
         <v>1.0800650000000001</v>
@@ -5844,12 +5850,12 @@
         <v>0.68423400000000001</v>
       </c>
       <c r="E229" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B230">
         <v>1.0068159999999999</v>
@@ -5861,12 +5867,12 @@
         <v>0.63403799999999999</v>
       </c>
       <c r="E230" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B231">
         <v>1.0743259999999999</v>
@@ -5878,12 +5884,12 @@
         <v>0.68342800000000004</v>
       </c>
       <c r="E231" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B232">
         <v>1.07338</v>
@@ -5895,12 +5901,12 @@
         <v>0.67988000000000004</v>
       </c>
       <c r="E232" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B233">
         <v>1.0858399999999999</v>
@@ -5912,12 +5918,12 @@
         <v>0.68703000000000003</v>
       </c>
       <c r="E233" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B234">
         <v>1.041936</v>
@@ -5929,12 +5935,12 @@
         <v>0.65914799999999996</v>
       </c>
       <c r="E234" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B235">
         <v>1.0939179999999999</v>
@@ -5946,12 +5952,12 @@
         <v>0.692326</v>
       </c>
       <c r="E235" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B236">
         <v>1.088098</v>
@@ -5963,12 +5969,12 @@
         <v>0.68858900000000001</v>
       </c>
       <c r="E236" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B237">
         <v>1.07423</v>
@@ -5980,12 +5986,12 @@
         <v>0.68098000000000003</v>
       </c>
       <c r="E237" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B238">
         <v>1.034044</v>
@@ -5997,12 +6003,12 @@
         <v>0.65027000000000001</v>
       </c>
       <c r="E238" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B239">
         <v>1.048076</v>
@@ -6014,12 +6020,12 @@
         <v>0.66148099999999999</v>
       </c>
       <c r="E239" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B240">
         <v>1.06132</v>
@@ -6031,12 +6037,12 @@
         <v>0.66971499999999995</v>
       </c>
       <c r="E240" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B241">
         <v>1.0818650000000001</v>
@@ -6048,12 +6054,12 @@
         <v>0.68081899999999995</v>
       </c>
       <c r="E241" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B242">
         <v>1.0562689999999999</v>
@@ -6065,12 +6071,12 @@
         <v>0.66856300000000002</v>
       </c>
       <c r="E242" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B243">
         <v>1.0336179999999999</v>
@@ -6082,12 +6088,12 @@
         <v>0.65369699999999997</v>
       </c>
       <c r="E243" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B244">
         <v>1.0690440000000001</v>
@@ -6099,12 +6105,12 @@
         <v>0.67659100000000005</v>
       </c>
       <c r="E244" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B245">
         <v>1.0507010000000001</v>
@@ -6116,12 +6122,12 @@
         <v>0.66383199999999998</v>
       </c>
       <c r="E245" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B246">
         <v>1.0520069999999999</v>
@@ -6133,12 +6139,12 @@
         <v>0.66256999999999999</v>
       </c>
       <c r="E246" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B247">
         <v>1.069053</v>
@@ -6150,12 +6156,12 @@
         <v>0.67434799999999995</v>
       </c>
       <c r="E247" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B248">
         <v>1.072638</v>
@@ -6167,12 +6173,12 @@
         <v>0.67337000000000002</v>
       </c>
       <c r="E248" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B249">
         <v>1.078122</v>
@@ -6184,12 +6190,12 @@
         <v>0.68289100000000003</v>
       </c>
       <c r="E249" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B250">
         <v>1.0659000000000001</v>
@@ -6201,12 +6207,12 @@
         <v>0.67578199999999999</v>
       </c>
       <c r="E250" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B251">
         <v>1.0633079999999999</v>
@@ -6218,12 +6224,12 @@
         <v>0.67203500000000005</v>
       </c>
       <c r="E251" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B252">
         <v>1.061685</v>
@@ -6235,12 +6241,12 @@
         <v>0.67011799999999999</v>
       </c>
       <c r="E252" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B253">
         <v>1.0585199999999999</v>
@@ -6252,12 +6258,12 @@
         <v>0.66475300000000004</v>
       </c>
       <c r="E253" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B254">
         <v>1.0885450000000001</v>
@@ -6269,12 +6275,12 @@
         <v>0.68637999999999999</v>
       </c>
       <c r="E254" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B255">
         <v>1.0426500000000001</v>
@@ -6286,12 +6292,12 @@
         <v>0.65805000000000002</v>
       </c>
       <c r="E255" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B256">
         <v>1.0419639999999999</v>
@@ -6303,12 +6309,12 @@
         <v>0.66078800000000004</v>
       </c>
       <c r="E256" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B257">
         <v>1.048767</v>
@@ -6320,12 +6326,12 @@
         <v>0.66482200000000002</v>
       </c>
       <c r="E257" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B258">
         <v>1.061283</v>
@@ -6337,12 +6343,12 @@
         <v>0.67155399999999998</v>
       </c>
       <c r="E258" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B259">
         <v>1.075415</v>
@@ -6354,12 +6360,12 @@
         <v>0.68290099999999998</v>
       </c>
       <c r="E259" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B260">
         <v>1.038427</v>
@@ -6371,12 +6377,12 @@
         <v>0.65712700000000002</v>
       </c>
       <c r="E260" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B261">
         <v>1.028141</v>
@@ -6388,12 +6394,12 @@
         <v>0.65217199999999997</v>
       </c>
       <c r="E261" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B262">
         <v>1.052303</v>
@@ -6405,12 +6411,12 @@
         <v>0.66474299999999997</v>
       </c>
       <c r="E262" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B263">
         <v>1.059769</v>
@@ -6422,12 +6428,12 @@
         <v>0.67018</v>
       </c>
       <c r="E263" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B264">
         <v>1.0428740000000001</v>
@@ -6439,12 +6445,12 @@
         <v>0.66541799999999995</v>
       </c>
       <c r="E264" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B265">
         <v>1.060014</v>
@@ -6456,12 +6462,12 @@
         <v>0.67418500000000003</v>
       </c>
       <c r="E265" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B266">
         <v>1.090924</v>
@@ -6473,12 +6479,12 @@
         <v>0.69228500000000004</v>
       </c>
       <c r="E266" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B267">
         <v>1.0306340000000001</v>
@@ -6490,12 +6496,12 @@
         <v>0.65191399999999999</v>
       </c>
       <c r="E267" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B268">
         <v>1.083985</v>
@@ -6507,12 +6513,12 @@
         <v>0.68480099999999999</v>
       </c>
       <c r="E268" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B269">
         <v>1.0626469999999999</v>
@@ -6524,12 +6530,12 @@
         <v>0.67186000000000001</v>
       </c>
       <c r="E269" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B270">
         <v>1.054189</v>
@@ -6541,12 +6547,12 @@
         <v>0.66745399999999999</v>
       </c>
       <c r="E270" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B271">
         <v>1.064592</v>
@@ -6558,12 +6564,12 @@
         <v>0.68124399999999996</v>
       </c>
       <c r="E271" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B272">
         <v>1.0446</v>
@@ -6575,12 +6581,12 @@
         <v>0.65996200000000005</v>
       </c>
       <c r="E272" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B273">
         <v>1.0699149999999999</v>
@@ -6592,12 +6598,12 @@
         <v>0.68395099999999998</v>
       </c>
       <c r="E273" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B274">
         <v>1.0607390000000001</v>
@@ -6609,12 +6615,12 @@
         <v>0.67212099999999997</v>
       </c>
       <c r="E274" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B275">
         <v>1.0604979999999999</v>
@@ -6626,12 +6632,12 @@
         <v>0.66904300000000005</v>
       </c>
       <c r="E275" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B276">
         <v>1.047838</v>
@@ -6643,12 +6649,12 @@
         <v>0.66270099999999998</v>
       </c>
       <c r="E276" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B277">
         <v>1.0407580000000001</v>
@@ -6660,12 +6666,12 @@
         <v>0.66130599999999995</v>
       </c>
       <c r="E277" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B278">
         <v>1.0622849999999999</v>
@@ -6677,12 +6683,12 @@
         <v>0.67324600000000001</v>
       </c>
       <c r="E278" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B279">
         <v>1.0578700000000001</v>
@@ -6694,12 +6700,12 @@
         <v>0.66969699999999999</v>
       </c>
       <c r="E279" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B280">
         <v>1.055728</v>
@@ -6711,12 +6717,12 @@
         <v>0.67257800000000001</v>
       </c>
       <c r="E280" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B281">
         <v>1.0646800000000001</v>
@@ -6728,12 +6734,12 @@
         <v>0.671871</v>
       </c>
       <c r="E281" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B282">
         <v>1.04128</v>
@@ -6745,12 +6751,12 @@
         <v>0.65856599999999998</v>
       </c>
       <c r="E282" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B283">
         <v>0.99959900000000002</v>
@@ -6762,12 +6768,12 @@
         <v>0.63420299999999996</v>
       </c>
       <c r="E283" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B284">
         <v>1.0519400000000001</v>
@@ -6779,12 +6785,12 @@
         <v>0.66389100000000001</v>
       </c>
       <c r="E284" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B285">
         <v>1.0271999999999999</v>
@@ -6796,12 +6802,12 @@
         <v>0.64929599999999998</v>
       </c>
       <c r="E285" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B286">
         <v>1.07002</v>
@@ -6813,12 +6819,12 @@
         <v>0.67924099999999998</v>
       </c>
       <c r="E286" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B287">
         <v>1.0413699999999999</v>
@@ -6830,12 +6836,12 @@
         <v>0.65851999999999999</v>
       </c>
       <c r="E287" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B288">
         <v>1.0474509999999999</v>
@@ -6847,12 +6853,12 @@
         <v>0.66355799999999998</v>
       </c>
       <c r="E288" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B289">
         <v>1.0968580000000001</v>
@@ -6864,12 +6870,12 @@
         <v>0.69991999999999999</v>
       </c>
       <c r="E289" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B290">
         <v>1.034249</v>
@@ -6881,12 +6887,12 @@
         <v>0.65057900000000002</v>
       </c>
       <c r="E290" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B291">
         <v>1.03891</v>
@@ -6898,12 +6904,12 @@
         <v>0.65443399999999996</v>
       </c>
       <c r="E291" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B292">
         <v>1.091302</v>
@@ -6915,12 +6921,12 @@
         <v>0.69517399999999996</v>
       </c>
       <c r="E292" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B293">
         <v>1.0337069999999999</v>
@@ -6932,12 +6938,12 @@
         <v>0.65313699999999997</v>
       </c>
       <c r="E293" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B294">
         <v>1.05968</v>
@@ -6949,12 +6955,12 @@
         <v>0.66796800000000001</v>
       </c>
       <c r="E294" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B295">
         <v>1.015382</v>
@@ -6966,12 +6972,12 @@
         <v>0.64212400000000003</v>
       </c>
       <c r="E295" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B296">
         <v>1.0549900000000001</v>
@@ -6983,12 +6989,12 @@
         <v>0.66658300000000004</v>
       </c>
       <c r="E296" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B297">
         <v>1.06121</v>
@@ -7000,12 +7006,12 @@
         <v>0.66964599999999996</v>
       </c>
       <c r="E297" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B298">
         <v>1.009708</v>
@@ -7017,12 +7023,12 @@
         <v>0.63993299999999997</v>
       </c>
       <c r="E298" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B299">
         <v>1.01823</v>
@@ -7034,12 +7040,12 @@
         <v>0.63832999999999995</v>
       </c>
       <c r="E299" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B300">
         <v>1.0587299999999999</v>
@@ -7051,12 +7057,12 @@
         <v>0.67273899999999998</v>
       </c>
       <c r="E300" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B301">
         <v>1.050697</v>
@@ -7068,12 +7074,12 @@
         <v>0.66291500000000003</v>
       </c>
       <c r="E301" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B302">
         <v>1.0648249999999999</v>
@@ -7085,12 +7091,12 @@
         <v>0.67303199999999996</v>
       </c>
       <c r="E302" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B303">
         <v>1.0417179999999999</v>
@@ -7102,12 +7108,12 @@
         <v>0.65821499999999999</v>
       </c>
       <c r="E303" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B304">
         <v>1.0666310000000001</v>
@@ -7119,12 +7125,12 @@
         <v>0.67251300000000003</v>
       </c>
       <c r="E304" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B305">
         <v>1.057831</v>
@@ -7136,12 +7142,12 @@
         <v>0.67115199999999997</v>
       </c>
       <c r="E305" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B306">
         <v>1.0529809999999999</v>
@@ -7153,12 +7159,12 @@
         <v>0.66832100000000005</v>
       </c>
       <c r="E306" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B307">
         <v>1.021509</v>
@@ -7170,12 +7176,12 @@
         <v>0.6421</v>
       </c>
       <c r="E307" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B308">
         <v>1.03609</v>
@@ -7187,12 +7193,12 @@
         <v>0.65471699999999999</v>
       </c>
       <c r="E308" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B309">
         <v>1.0634300000000001</v>
@@ -7204,12 +7210,12 @@
         <v>0.677755</v>
       </c>
       <c r="E309" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B310">
         <v>1.0370600000000001</v>
@@ -7221,12 +7227,12 @@
         <v>0.65405100000000005</v>
       </c>
       <c r="E310" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B311">
         <v>1.0543309999999999</v>
@@ -7238,12 +7244,12 @@
         <v>0.66672699999999996</v>
       </c>
       <c r="E311" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B312">
         <v>0.99036400000000002</v>
@@ -7255,12 +7261,12 @@
         <v>0.62646400000000002</v>
       </c>
       <c r="E312" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B313">
         <v>1.0068900000000001</v>
@@ -7272,12 +7278,12 @@
         <v>0.635629</v>
       </c>
       <c r="E313" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B314">
         <v>1.04491</v>
@@ -7289,12 +7295,12 @@
         <v>0.66107300000000002</v>
       </c>
       <c r="E314" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B315">
         <v>1.033677</v>
@@ -7306,12 +7312,12 @@
         <v>0.65855200000000003</v>
       </c>
       <c r="E315" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B316">
         <v>1.0788219999999999</v>
@@ -7323,12 +7329,12 @@
         <v>0.68292299999999995</v>
       </c>
       <c r="E316" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B317">
         <v>1.05975</v>
@@ -7340,12 +7346,12 @@
         <v>0.67196299999999998</v>
       </c>
       <c r="E317" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B318">
         <v>1.047126</v>
@@ -7357,12 +7363,12 @@
         <v>0.66580700000000004</v>
       </c>
       <c r="E318" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B319">
         <v>1.0785640000000001</v>
@@ -7374,12 +7380,12 @@
         <v>0.68354400000000004</v>
       </c>
       <c r="E319" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B320">
         <v>1.064262</v>
@@ -7391,12 +7397,12 @@
         <v>0.674064</v>
       </c>
       <c r="E320" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B321">
         <v>1.030516</v>
@@ -7408,12 +7414,12 @@
         <v>0.65529599999999999</v>
       </c>
       <c r="E321" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B322">
         <v>0.91517999999999999</v>
@@ -7425,12 +7431,12 @@
         <v>0.57771899999999998</v>
       </c>
       <c r="E322" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B323">
         <v>1.0163469999999999</v>
@@ -7442,12 +7448,12 @@
         <v>0.63712500000000005</v>
       </c>
       <c r="E323" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B324">
         <v>1.0218</v>
@@ -7459,12 +7465,12 @@
         <v>0.64842599999999995</v>
       </c>
       <c r="E324" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B325">
         <v>1.0562819999999999</v>
@@ -7476,12 +7482,12 @@
         <v>0.66953200000000002</v>
       </c>
       <c r="E325" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B326">
         <v>1.0095940000000001</v>
@@ -7493,12 +7499,12 @@
         <v>0.63893200000000006</v>
       </c>
       <c r="E326" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B327">
         <v>1.0274639999999999</v>
@@ -7510,12 +7516,12 @@
         <v>0.65280700000000003</v>
       </c>
       <c r="E327" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B328">
         <v>1.0141249999999999</v>
@@ -7527,12 +7533,12 @@
         <v>0.644285</v>
       </c>
       <c r="E328" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B329">
         <v>1.0267390000000001</v>
@@ -7544,12 +7550,12 @@
         <v>0.64700500000000005</v>
       </c>
       <c r="E329" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B330">
         <v>1.0036210000000001</v>
@@ -7561,12 +7567,12 @@
         <v>0.63823099999999999</v>
       </c>
       <c r="E330" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B331">
         <v>1.010399</v>
@@ -7578,15 +7584,7 @@
         <v>0.64027199999999995</v>
       </c>
       <c r="E331" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>354</v>
-      </c>
-      <c r="D332">
-        <v>0.68586800000000003</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
